--- a/KNK업무시스템구축_엑셀/V2/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="D7" s="51" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C10" s="59" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C15" s="50" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C18" s="59" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="D18" s="60" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C19" s="50" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="D19" s="51" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C20" s="59" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="D20" s="60" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="D21" s="51" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C26" s="59" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="D26" s="60" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="D7" s="50" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="D8" s="59" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="C10" s="59" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="D10" s="59" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="D11" s="50" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="D13" s="50" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="C15" s="50" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="D15" s="50" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="C18" s="59" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="D18" s="59" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C19" s="50" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="D19" s="50" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C20" s="59" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="D20" s="59" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="D21" s="50" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="D23" s="50" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="C26" s="59" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="D26" s="59" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C5" s="50" t="inlineStr">
         <is>
-          <t>M-260105-3</t>
+          <t>M-260105-2</t>
         </is>
       </c>
       <c r="D5" s="51" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
-          <t>M-251127-2</t>
+          <t>M-251127-1</t>
         </is>
       </c>
       <c r="D7" s="51" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>M-251127-3</t>
+          <t>M-251127-2</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C9" s="50" t="inlineStr">
         <is>
-          <t>M-251127-4</t>
+          <t>M-251127-3</t>
         </is>
       </c>
       <c r="D9" s="51" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C10" s="59" t="inlineStr">
         <is>
-          <t>M-251127-5</t>
+          <t>M-251127-4</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>M-251127-6</t>
+          <t>M-251127-5</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="D7" s="50" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="D8" s="59" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="C10" s="59" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="D10" s="59" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="D11" s="50" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="D13" s="50" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="C15" s="50" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="D15" s="50" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="C18" s="59" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="D18" s="59" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="C19" s="50" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="D19" s="50" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C20" s="59" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="D20" s="59" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="D21" s="50" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="D23" s="50" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="C26" s="59" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="D26" s="59" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C30" s="59" t="inlineStr">
         <is>
-          <t>M-251127-2</t>
+          <t>M-251127-1</t>
         </is>
       </c>
       <c r="D30" s="59" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>M-251127-3</t>
+          <t>M-251127-2</t>
         </is>
       </c>
       <c r="D31" s="50" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="C32" s="59" t="inlineStr">
         <is>
-          <t>M-251127-4</t>
+          <t>M-251127-3</t>
         </is>
       </c>
       <c r="D32" s="59" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>M-251127-5</t>
+          <t>M-251127-4</t>
         </is>
       </c>
       <c r="D33" s="50" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C34" s="59" t="inlineStr">
         <is>
-          <t>M-251127-6</t>
+          <t>M-251127-5</t>
         </is>
       </c>
       <c r="D34" s="59" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="C6" s="59" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="D6" s="59" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="D7" s="50" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="D8" s="59" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C9" s="50" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="D9" s="50" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="D11" s="50" t="inlineStr">
@@ -16055,7 +16055,7 @@
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="D13" s="50" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="C14" s="59" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="D14" s="59" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="C15" s="50" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="D15" s="50" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="D16" s="59" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="C17" s="50" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="D17" s="50" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="C18" s="59" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="D18" s="59" t="inlineStr">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="C20" s="59" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="D20" s="59" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="D23" s="50" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="B8" s="59" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="C8" s="59" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="B9" s="50" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="C9" s="50" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="B11" s="50" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="C11" s="50" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="B12" s="59" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="C12" s="59" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="B13" s="50" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="C13" s="50" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="B14" s="59" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="C14" s="59" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="B18" s="59" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="C18" s="59" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="B19" s="50" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="C19" s="50" t="inlineStr">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="B20" s="59" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="C20" s="59" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="B21" s="50" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="C21" s="50" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="B22" s="59" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="C22" s="59" t="inlineStr">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="B23" s="50" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="C23" s="50" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="B25" s="50" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="C25" s="50" t="inlineStr">
